--- a/experiment_results/combined_sweep/rtt_bursts_S3_atk5pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S3_atk5pct_wu500000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:010.1</t>
+          <t>00:010.0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.2</t>
+          <t>00:019.6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>119.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>87.69</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>167494</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -583,34 +583,34 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.2</t>
+          <t>00:030.0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10821</t>
+          <t>336127</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -640,34 +640,34 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:039.6</t>
+          <t>00:039.9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13716</t>
+          <t>365086</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:049.9</t>
+          <t>00:050.2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21904</t>
+          <t>399819</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:000.4</t>
+          <t>00:059.8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50933</t>
+          <t>411622</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -811,29 +811,29 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:009.8</t>
+          <t>01:010.3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>80409</t>
+          <t>421772</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -868,34 +868,34 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:019.7</t>
+          <t>01:019.9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>88834</t>
+          <t>437058</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.0</t>
+          <t>01:029.5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>63.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>12.60</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>111515</t>
+          <t>458788</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -982,34 +982,34 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:039.9</t>
+          <t>01:040.5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.60</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>138707</t>
+          <t>472851</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1039,34 +1039,34 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.1</t>
+          <t>01:049.8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>124.7</t>
+          <t>62.9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>16.06</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>201202</t>
+          <t>493793</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1096,34 +1096,34 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:000.1</t>
+          <t>02:000.7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>123.4</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>255524</t>
+          <t>518130</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1153,34 +1153,34 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.1</t>
+          <t>02:010.2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,17 +1190,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>260054</t>
+          <t>527069</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:020.0</t>
+          <t>02:019.8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>7.18</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>264506</t>
+          <t>538113</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1279,22 +1279,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>258769</t>
+          <t>551430</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1336,22 +1336,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>249897</t>
+          <t>545360</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:049.9</t>
+          <t>02:049.4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8.41</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>238623</t>
+          <t>523734</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.4</t>
+          <t>02:054.6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,17 +1475,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>231630</t>
+          <t>514892</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1494,63 +1494,6 @@
         </is>
       </c>
       <c r="K19" t="inlineStr">
-        <is>
-          <t>Normal/Residual</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>03:000.3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>231293</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
         <is>
           <t>Normal/Residual</t>
         </is>

--- a/experiment_results/combined_sweep/rtt_bursts_S3_atk5pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S3_atk5pct_wu500000.xlsx
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:019.6</t>
+          <t>00:019.8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>119.3</t>
+          <t>177.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>87.69</t>
+          <t>78.51</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>167494</t>
+          <t>220462</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.0</t>
+          <t>00:030.5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>125.2</t>
+          <t>190.8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>336127</t>
+          <t>469427</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:039.9</t>
+          <t>00:040.3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>365086</t>
+          <t>497701</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.2</t>
+          <t>00:050.0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>399819</t>
+          <t>500793</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,22 +766,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>14.14</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>411622</t>
+          <t>516049</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.3</t>
+          <t>01:009.7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>10.70</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>421772</t>
+          <t>539131</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:019.9</t>
+          <t>01:020.2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>145.9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12.59</t>
+          <t>25.83</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>437058</t>
+          <t>621372</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -925,34 +925,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:029.5</t>
+          <t>01:030.4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>12.60</t>
+          <t>12.56</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>458788</t>
+          <t>711065</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -982,34 +982,34 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.5</t>
+          <t>01:040.1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>472851</t>
+          <t>753614</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.8</t>
+          <t>01:051.0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>62.9</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>493793</t>
+          <t>792765</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:000.7</t>
+          <t>01:059.7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>518130</t>
+          <t>827659</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.2</t>
+          <t>02:009.8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>527069</t>
+          <t>870841</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.8</t>
+          <t>02:018.9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>538113</t>
+          <t>909334</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.0</t>
+          <t>02:030.1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>551430</t>
+          <t>941623</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.9</t>
+          <t>02:039.8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>545360</t>
+          <t>950789</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:049.4</t>
+          <t>02:049.9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>523734</t>
+          <t>931867</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:054.6</t>
+          <t>02:055.0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>514892</t>
+          <t>921130</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
